--- a/sheets/민요/검수/는실 타령-1.xlsx
+++ b/sheets/민요/검수/는실 타령-1.xlsx
@@ -590,10 +590,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/는실 타령-1.xlsx
+++ b/sheets/민요/검수/는실 타령-1.xlsx
@@ -536,17 +536,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -663,7 +663,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -713,6 +713,42 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2173,240 +2209,240 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="40.82" customHeight="true">
+      <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B3" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="17" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B4" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B5" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B7" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="19" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B9" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="20" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.88" customHeight="true">
+      <c r="B10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="21" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2416,7 +2452,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="98"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/는실 타령-1.xlsx
+++ b/sheets/민요/검수/는실 타령-1.xlsx
@@ -2215,13 +2215,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="14" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="13" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="14" width="6"/>
   </cols>
   <sheetData>
